--- a/data/trans_orig/P5702-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5702-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir ayuda en asuntos relacionados con mi casa en 2007</t>
+          <t>Población según la frecuencia de recibir ayuda en asuntos relacionados con mi casa en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>274850</t>
+          <t>275127</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>327641</t>
+          <t>326214</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>228041</t>
+          <t>226727</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>276171</t>
+          <t>275223</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>512257</t>
+          <t>516618</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>586359</t>
+          <t>591436</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,78%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>222471</t>
+          <t>223926</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>271681</t>
+          <t>272445</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>177402</t>
+          <t>178696</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>223512</t>
+          <t>225989</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>412203</t>
+          <t>415066</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>483335</t>
+          <t>482790</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>101751</t>
+          <t>103976</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>142604</t>
+          <t>142617</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>118876</t>
+          <t>119691</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160899</t>
+          <t>163131</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>231406</t>
+          <t>233855</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>288386</t>
+          <t>290008</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14811</t>
+          <t>13800</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35387</t>
+          <t>35465</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71204</t>
+          <t>72457</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107017</t>
+          <t>106956</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92433</t>
+          <t>93201</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>133478</t>
+          <t>136754</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5810</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18316</t>
+          <t>17853</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19549</t>
+          <t>20093</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>457895</t>
+          <t>457213</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>518434</t>
+          <t>521032</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>386260</t>
+          <t>386798</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>452719</t>
+          <t>451996</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>860246</t>
+          <t>860690</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>949045</t>
+          <t>951639</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,3%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>229249</t>
+          <t>230063</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>286363</t>
+          <t>285367</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>227057</t>
+          <t>221944</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>283173</t>
+          <t>278600</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>466923</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>547435</t>
+          <t>543928</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>125558</t>
+          <t>124643</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>173934</t>
+          <t>170003</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>136162</t>
+          <t>138070</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183871</t>
+          <t>185264</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>275416</t>
+          <t>272701</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>340851</t>
+          <t>340548</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35451</t>
+          <t>36753</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65268</t>
+          <t>63840</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85576</t>
+          <t>86684</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125343</t>
+          <t>128016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132313</t>
+          <t>132969</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182025</t>
+          <t>183472</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14365</t>
+          <t>13831</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34536</t>
+          <t>34575</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21310</t>
+          <t>21755</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44295</t>
+          <t>43646</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40685</t>
+          <t>38544</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>69508</t>
+          <t>70936</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>331761</t>
+          <t>331405</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>386244</t>
+          <t>383545</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>314226</t>
+          <t>314344</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>364710</t>
+          <t>362931</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>658574</t>
+          <t>659812</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>737110</t>
+          <t>734173</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,89%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147622</t>
+          <t>146988</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>192945</t>
+          <t>192875</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>133361</t>
+          <t>132678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174292</t>
+          <t>177027</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>291108</t>
+          <t>291040</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>354047</t>
+          <t>355229</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>80738</t>
+          <t>82260</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>117455</t>
+          <t>118844</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>92550</t>
+          <t>93698</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131106</t>
+          <t>132634</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>181795</t>
+          <t>184590</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>235039</t>
+          <t>236568</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31149</t>
+          <t>30734</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57057</t>
+          <t>58594</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54343</t>
+          <t>54792</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86324</t>
+          <t>85892</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92380</t>
+          <t>93247</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>133372</t>
+          <t>133485</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21141</t>
+          <t>21526</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>20261</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>14021</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>35136</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>439685</t>
+          <t>440100</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>498736</t>
+          <t>502776</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>446230</t>
+          <t>446091</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>509411</t>
+          <t>508998</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>905104</t>
+          <t>904526</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>992834</t>
+          <t>994055</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,18%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233589</t>
+          <t>236439</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>288519</t>
+          <t>290063</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>242851</t>
+          <t>245520</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>300250</t>
+          <t>302556</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>491525</t>
+          <t>493049</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>570449</t>
+          <t>573605</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>115146</t>
+          <t>113626</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>158483</t>
+          <t>155332</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>128110</t>
+          <t>127629</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>173438</t>
+          <t>173833</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>251475</t>
+          <t>252024</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>315301</t>
+          <t>316185</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>44082</t>
+          <t>44433</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>72261</t>
+          <t>73461</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>93391</t>
+          <t>92204</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>135429</t>
+          <t>133808</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>147541</t>
+          <t>146450</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>197483</t>
+          <t>198567</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11467</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>31150</t>
+          <t>33165</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17922</t>
+          <t>17984</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>40373</t>
+          <t>40100</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>34964</t>
+          <t>34378</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>64761</t>
+          <t>63005</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1558102</t>
+          <t>1552239</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1679440</t>
+          <t>1671541</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1424769</t>
+          <t>1435877</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1548813</t>
+          <t>1545112</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3014489</t>
+          <t>3022105</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3179413</t>
+          <t>3187241</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,89%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>882115</t>
+          <t>884795</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>983114</t>
+          <t>985371</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>825791</t>
+          <t>824918</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>931020</t>
+          <t>922343</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1739609</t>
+          <t>1737396</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1886414</t>
+          <t>1881853</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>463830</t>
+          <t>461265</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>547856</t>
+          <t>544628</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>514660</t>
+          <t>516506</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>602312</t>
+          <t>604491</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1000470</t>
+          <t>1003431</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1123185</t>
+          <t>1125701</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>145971</t>
+          <t>144930</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>198125</t>
+          <t>197410</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>338938</t>
+          <t>341288</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>414674</t>
+          <t>419477</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>502714</t>
+          <t>501855</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>595261</t>
+          <t>595201</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>43007</t>
+          <t>42747</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>75324</t>
+          <t>76429</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>62614</t>
+          <t>62588</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>98484</t>
+          <t>97855</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>112189</t>
+          <t>114849</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>159392</t>
+          <t>162711</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir ayuda en asuntos relacionados con mi casa en 2012</t>
+          <t>Población según la frecuencia de recibir ayuda en asuntos relacionados con mi casa en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>375989</t>
+          <t>375419</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>430847</t>
+          <t>429864</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>294002</t>
+          <t>293991</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>348006</t>
+          <t>346773</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>686554</t>
+          <t>686541</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>763774</t>
+          <t>763331</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,57%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>137609</t>
+          <t>141796</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>185375</t>
+          <t>186356</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>175297</t>
+          <t>176208</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>226511</t>
+          <t>225520</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>328398</t>
+          <t>327645</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>394532</t>
+          <t>394076</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,17%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77170</t>
+          <t>75583</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115097</t>
+          <t>112478</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61166</t>
+          <t>62923</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>95553</t>
+          <t>96641</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146996</t>
+          <t>145814</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>200603</t>
+          <t>199367</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15557</t>
+          <t>15593</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34355</t>
+          <t>33119</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47106</t>
+          <t>47097</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77599</t>
+          <t>79536</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68642</t>
+          <t>68250</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104656</t>
+          <t>104476</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>10484</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28166</t>
+          <t>29075</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,82 +4842,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>38097</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>27837</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>52247</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>7,5%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>56110</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>42420</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>72278</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>4,01%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>38097</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>27842</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>53144</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>56110</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>42557</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>72688</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>489766</t>
+          <t>488548</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>556423</t>
+          <t>559157</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>416140</t>
+          <t>414420</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>483431</t>
+          <t>482490</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>926911</t>
+          <t>927437</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1022595</t>
+          <t>1020741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,86%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>249702</t>
+          <t>243258</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310578</t>
+          <t>305467</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>252895</t>
+          <t>251915</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>311478</t>
+          <t>310430</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>513185</t>
+          <t>516881</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>599399</t>
+          <t>601243</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>113973</t>
+          <t>114835</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>158927</t>
+          <t>160391</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145132</t>
+          <t>144271</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>194800</t>
+          <t>195438</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>273413</t>
+          <t>272325</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>342354</t>
+          <t>339665</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51978</t>
+          <t>51877</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86487</t>
+          <t>87871</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72771</t>
+          <t>74427</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>110001</t>
+          <t>113932</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132809</t>
+          <t>134034</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>185958</t>
+          <t>184711</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22455</t>
+          <t>21457</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27514</t>
+          <t>28534</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54843</t>
+          <t>56119</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39207</t>
+          <t>37443</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70544</t>
+          <t>68552</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>366489</t>
+          <t>365821</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>422011</t>
+          <t>424597</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>326159</t>
+          <t>326662</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>385706</t>
+          <t>385912</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>710856</t>
+          <t>707376</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>792304</t>
+          <t>787010</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,39%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>150470</t>
+          <t>152600</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199905</t>
+          <t>201341</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>174832</t>
+          <t>174054</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>226287</t>
+          <t>223334</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>339280</t>
+          <t>338367</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>405962</t>
+          <t>411721</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>89747</t>
+          <t>90007</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>131845</t>
+          <t>129818</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>90240</t>
+          <t>89848</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>129296</t>
+          <t>132797</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>191539</t>
+          <t>189603</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>250443</t>
+          <t>250582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36272</t>
+          <t>34631</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64425</t>
+          <t>63245</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62405</t>
+          <t>60235</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>95291</t>
+          <t>95529</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102808</t>
+          <t>103921</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>147742</t>
+          <t>146762</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>16857</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42952</t>
+          <t>41072</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25883</t>
+          <t>26840</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52185</t>
+          <t>52574</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49289</t>
+          <t>48564</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86545</t>
+          <t>83724</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>432935</t>
+          <t>432839</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>495831</t>
+          <t>495596</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>406901</t>
+          <t>411104</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>472644</t>
+          <t>469594</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>857888</t>
+          <t>857876</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>951064</t>
+          <t>945967</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,38%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>258395</t>
+          <t>254596</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>316942</t>
+          <t>314584</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>295599</t>
+          <t>295345</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>354147</t>
+          <t>353518</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>567542</t>
+          <t>569051</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>650160</t>
+          <t>652398</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>94688</t>
+          <t>96225</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>137377</t>
+          <t>136948</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>121586</t>
+          <t>120377</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>164316</t>
+          <t>167119</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>226361</t>
+          <t>223202</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>289293</t>
+          <t>287301</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>45898</t>
+          <t>47917</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>76743</t>
+          <t>78640</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>68701</t>
+          <t>68504</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>107388</t>
+          <t>103344</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>125135</t>
+          <t>123199</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>170575</t>
+          <t>170695</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13547</t>
+          <t>13583</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33185</t>
+          <t>34004</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44924</t>
+          <t>44545</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>74826</t>
+          <t>74462</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>63432</t>
+          <t>65105</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>96784</t>
+          <t>100823</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1722695</t>
+          <t>1720768</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1841074</t>
+          <t>1843055</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1499127</t>
+          <t>1500951</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1625915</t>
+          <t>1622202</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3268916</t>
+          <t>3262648</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3442014</t>
+          <t>3431605</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,21%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>853003</t>
+          <t>847551</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>956704</t>
+          <t>955770</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>953588</t>
+          <t>955232</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1064443</t>
+          <t>1064658</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1833939</t>
+          <t>1831517</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1987923</t>
+          <t>1989142</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>412493</t>
+          <t>415566</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>494303</t>
+          <t>497166</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>457151</t>
+          <t>453479</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>540270</t>
+          <t>540638</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>895782</t>
+          <t>894480</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1013228</t>
+          <t>1017251</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>172466</t>
+          <t>171682</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>228868</t>
+          <t>231044</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>280108</t>
+          <t>278025</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>350269</t>
+          <t>346866</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>468644</t>
+          <t>472649</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>561298</t>
+          <t>560237</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>61069</t>
+          <t>61789</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>101146</t>
+          <t>101645</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>149659</t>
+          <t>150141</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>202701</t>
+          <t>202524</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>223304</t>
+          <t>223751</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>289360</t>
+          <t>288009</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir ayuda en asuntos relacionados con mi casa en 2016</t>
+          <t>Población según la frecuencia de recibir ayuda en asuntos relacionados con mi casa en 2016 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>272401</t>
+          <t>274538</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>324803</t>
+          <t>325216</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>217469</t>
+          <t>218002</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>265684</t>
+          <t>267515</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>504328</t>
+          <t>504279</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>577910</t>
+          <t>576105</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,85%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>195714</t>
+          <t>195408</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>245189</t>
+          <t>245922</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>203188</t>
+          <t>201423</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>252432</t>
+          <t>252160</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>409568</t>
+          <t>413824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>476408</t>
+          <t>481561</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80072</t>
+          <t>81150</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>116930</t>
+          <t>117335</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>107863</t>
+          <t>105206</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>146076</t>
+          <t>145148</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>198524</t>
+          <t>197810</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>252897</t>
+          <t>251056</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40305</t>
+          <t>39180</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68667</t>
+          <t>67735</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>39947</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70403</t>
+          <t>69048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87247</t>
+          <t>87303</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>128197</t>
+          <t>128008</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11085</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18659</t>
+          <t>17413</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39219</t>
+          <t>38152</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20903</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41951</t>
+          <t>45420</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>418396</t>
+          <t>413051</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>479595</t>
+          <t>482603</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>365214</t>
+          <t>362322</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>427358</t>
+          <t>427417</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>801003</t>
+          <t>797127</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>893903</t>
+          <t>888081</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>329749</t>
+          <t>329292</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>391814</t>
+          <t>394507</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325758</t>
+          <t>327146</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>389473</t>
+          <t>390186</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>672972</t>
+          <t>676378</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>762319</t>
+          <t>761235</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>134191</t>
+          <t>133386</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>179626</t>
+          <t>181118</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>147212</t>
+          <t>147209</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>196195</t>
+          <t>197949</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>293643</t>
+          <t>294178</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>361999</t>
+          <t>359659</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26770</t>
+          <t>26570</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52903</t>
+          <t>53860</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76051</t>
+          <t>75606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112484</t>
+          <t>113272</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108254</t>
+          <t>108579</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155213</t>
+          <t>154743</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27487</t>
+          <t>28478</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19287</t>
+          <t>17957</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40958</t>
+          <t>40742</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33439</t>
+          <t>32302</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61325</t>
+          <t>58797</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>279383</t>
+          <t>281631</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>332631</t>
+          <t>337210</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>263853</t>
+          <t>262163</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>319278</t>
+          <t>316261</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>555412</t>
+          <t>558564</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>632818</t>
+          <t>634621</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>232156</t>
+          <t>231077</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>282155</t>
+          <t>284524</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>236923</t>
+          <t>234742</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>291311</t>
+          <t>290401</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>482129</t>
+          <t>484001</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>558595</t>
+          <t>557059</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,2%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>136016</t>
+          <t>133221</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>179033</t>
+          <t>180166</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>146708</t>
+          <t>148240</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>193517</t>
+          <t>197057</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>296061</t>
+          <t>295684</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>366669</t>
+          <t>362138</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19848</t>
+          <t>20239</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43417</t>
+          <t>43265</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24629</t>
+          <t>24957</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48016</t>
+          <t>48589</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50823</t>
+          <t>50483</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83506</t>
+          <t>83121</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13855</t>
+          <t>14357</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33449</t>
+          <t>32801</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18482</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40399</t>
+          <t>40817</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>368044</t>
+          <t>368991</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>428515</t>
+          <t>428392</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>387681</t>
+          <t>388385</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>455407</t>
+          <t>454213</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>771150</t>
+          <t>779857</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>866895</t>
+          <t>863663</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,66%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>271146</t>
+          <t>269653</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>331636</t>
+          <t>327365</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>286103</t>
+          <t>284379</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>346524</t>
+          <t>345386</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>576178</t>
+          <t>573822</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>662064</t>
+          <t>651754</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>137153</t>
+          <t>136672</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>180516</t>
+          <t>182058</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>138686</t>
+          <t>140301</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>190424</t>
+          <t>188524</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>287959</t>
+          <t>289248</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>356914</t>
+          <t>354675</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36515</t>
+          <t>36223</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>62578</t>
+          <t>65373</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72532</t>
+          <t>72777</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>114386</t>
+          <t>111877</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>117475</t>
+          <t>118258</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>164958</t>
+          <t>165131</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20414</t>
+          <t>19814</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43079</t>
+          <t>42583</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37980</t>
+          <t>37736</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67084</t>
+          <t>66204</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>64887</t>
+          <t>64674</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>102347</t>
+          <t>101121</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1394817</t>
+          <t>1397430</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1513585</t>
+          <t>1518844</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1290255</t>
+          <t>1286044</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1402874</t>
+          <t>1404218</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2721921</t>
+          <t>2709268</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2881360</t>
+          <t>2886524</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,67%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1086387</t>
+          <t>1075684</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1196289</t>
+          <t>1191980</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1104446</t>
+          <t>1102896</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1216599</t>
+          <t>1214845</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2210812</t>
+          <t>2218121</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2369323</t>
+          <t>2380763</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,37%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>528931</t>
+          <t>524017</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>620605</t>
+          <t>617280</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>583102</t>
+          <t>581978</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>675032</t>
+          <t>673659</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1137378</t>
+          <t>1137275</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1262933</t>
+          <t>1265182</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>144451</t>
+          <t>143340</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>194837</t>
+          <t>195723</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>244480</t>
+          <t>241627</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>309019</t>
+          <t>307298</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>404543</t>
+          <t>407101</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>491628</t>
+          <t>487219</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>45051</t>
+          <t>44806</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>76651</t>
+          <t>75097</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,82 +11212,82 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>127062</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>105625</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>150510</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>186230</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>156460</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>213448</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>2,26%</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>127062</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>107731</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>150876</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>186230</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>160660</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>215218</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir ayuda en asuntos relacionados con mi casa en 2023</t>
+          <t>Población según la frecuencia de recibir ayuda en asuntos relacionados con mi casa en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>343408</t>
+          <t>339583</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>395780</t>
+          <t>393945</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>334461</t>
+          <t>338031</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>375132</t>
+          <t>377379</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>691491</t>
+          <t>692120</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>758388</t>
+          <t>759717</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,07%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>140367</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>183780</t>
+          <t>185744</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>180362</t>
+          <t>178368</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>216000</t>
+          <t>215055</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>328680</t>
+          <t>331197</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>388864</t>
+          <t>389343</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55595</t>
+          <t>55662</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87781</t>
+          <t>89490</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>65296</t>
+          <t>65116</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>88947</t>
+          <t>87943</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>127978</t>
+          <t>128242</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>167925</t>
+          <t>168143</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15214</t>
+          <t>14811</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31760</t>
+          <t>32159</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26422</t>
+          <t>26345</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43480</t>
+          <t>43894</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46168</t>
+          <t>45298</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70621</t>
+          <t>68846</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19101</t>
+          <t>18855</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15473</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14905</t>
+          <t>15397</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29119</t>
+          <t>29695</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>664934</t>
+          <t>658971</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>960448</t>
+          <t>990557</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>484906</t>
+          <t>483267</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>537642</t>
+          <t>537218</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1167423</t>
+          <t>1167664</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1566306</t>
+          <t>1587735</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>73,99%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>159820</t>
+          <t>140107</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>367310</t>
+          <t>367228</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>240088</t>
+          <t>241818</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>286141</t>
+          <t>285451</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>366775</t>
+          <t>360565</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>624298</t>
+          <t>624434</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38640</t>
+          <t>35172</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100433</t>
+          <t>101212</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>91602</t>
+          <t>93030</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>122327</t>
+          <t>123160</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>123042</t>
+          <t>115176</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>212448</t>
+          <t>215376</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16389</t>
+          <t>15338</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50591</t>
+          <t>50073</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44010</t>
+          <t>43542</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67765</t>
+          <t>69331</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59675</t>
+          <t>61199</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108582</t>
+          <t>110794</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32299</t>
+          <t>32799</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14485</t>
+          <t>14239</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34084</t>
+          <t>32759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25994</t>
+          <t>26303</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56907</t>
+          <t>57413</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>360784</t>
+          <t>360349</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>421537</t>
+          <t>422831</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>347431</t>
+          <t>346639</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>430073</t>
+          <t>428945</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>725773</t>
+          <t>726446</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>820202</t>
+          <t>817447</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>178042</t>
+          <t>177548</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>231808</t>
+          <t>233160</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>195706</t>
+          <t>195387</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>254668</t>
+          <t>254719</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>389630</t>
+          <t>393649</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>469441</t>
+          <t>472992</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59812</t>
+          <t>58894</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>98406</t>
+          <t>99104</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53212</t>
+          <t>54220</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>89795</t>
+          <t>91438</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,47 +13299,47 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
+          <t>12,57%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>147086</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>122413</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>176425</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>10,29%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>8,56%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
           <t>12,34%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>147086</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>121924</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>175538</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15130</t>
+          <t>15005</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33454</t>
+          <t>33275</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27659</t>
+          <t>28083</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49591</t>
+          <t>49250</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48688</t>
+          <t>49643</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75701</t>
+          <t>76576</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13889</t>
+          <t>14171</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,82 +13490,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>12596</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>7979</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>19582</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>20021</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>13237</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>28375</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>1,98%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>12596</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>7745</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>19551</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>20021</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>13484</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>29408</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>532023</t>
+          <t>529999</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>594732</t>
+          <t>591981</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>580903</t>
+          <t>581365</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>719411</t>
+          <t>709823</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1134489</t>
+          <t>1135959</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1289054</t>
+          <t>1281686</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,64%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>164028</t>
+          <t>166537</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>214149</t>
+          <t>215363</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>191563</t>
+          <t>191568</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>267788</t>
+          <t>267542</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>378005</t>
+          <t>373775</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>468332</t>
+          <t>465491</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>86374</t>
+          <t>84955</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>124361</t>
+          <t>125374</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>90222</t>
+          <t>87342</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>133135</t>
+          <t>131740</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>185682</t>
+          <t>187902</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>245895</t>
+          <t>245043</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32793</t>
+          <t>33071</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56474</t>
+          <t>57060</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54082</t>
+          <t>55206</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>82915</t>
+          <t>85190</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>94794</t>
+          <t>93667</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>134824</t>
+          <t>130487</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18023</t>
+          <t>17176</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36136</t>
+          <t>35799</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33606</t>
+          <t>33118</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66818</t>
+          <t>63517</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>56436</t>
+          <t>57267</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>93178</t>
+          <t>91683</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1982208</t>
+          <t>1989083</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2413625</t>
+          <t>2438418</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1802709</t>
+          <t>1805936</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1986352</t>
+          <t>1985492</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3821940</t>
+          <t>3823419</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4315190</t>
+          <t>4325219</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,7%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>643443</t>
+          <t>630210</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>916751</t>
+          <t>915099</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>861113</t>
+          <t>855267</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>978054</t>
+          <t>975872</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1548846</t>
+          <t>1542117</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1861731</t>
+          <t>1862232</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>254777</t>
+          <t>249390</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>369722</t>
+          <t>365875</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>334751</t>
+          <t>333724</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>401311</t>
+          <t>400651</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>610948</t>
+          <t>604719</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>746317</t>
+          <t>746805</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>94680</t>
+          <t>94461</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>145841</t>
+          <t>144146</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>174030</t>
+          <t>175532</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>221512</t>
+          <t>221134</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>278035</t>
+          <t>278291</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>351862</t>
+          <t>356551</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>49165</t>
+          <t>48460</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>84582</t>
+          <t>81893</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>73050</t>
+          <t>72890</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>110667</t>
+          <t>108566</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>129635</t>
+          <t>127982</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>183619</t>
+          <t>181754</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P5702-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5702-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>275127</t>
+          <t>274188</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>326214</t>
+          <t>325380</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>226727</t>
+          <t>224714</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>275223</t>
+          <t>277387</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>516618</t>
+          <t>516791</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>591436</t>
+          <t>585211</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>223926</t>
+          <t>224207</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272445</t>
+          <t>269725</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178696</t>
+          <t>176024</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>225989</t>
+          <t>225167</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>415066</t>
+          <t>414864</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>482790</t>
+          <t>482738</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103976</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>142617</t>
+          <t>144220</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>119691</t>
+          <t>118519</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>163131</t>
+          <t>159131</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>233855</t>
+          <t>232169</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>290008</t>
+          <t>287584</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>14950</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35465</t>
+          <t>34293</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72457</t>
+          <t>73011</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106956</t>
+          <t>107569</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93201</t>
+          <t>92627</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136754</t>
+          <t>135353</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4556</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17853</t>
+          <t>18239</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5756</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20093</t>
+          <t>22063</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>457213</t>
+          <t>457986</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>521032</t>
+          <t>520778</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>386798</t>
+          <t>388465</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>451996</t>
+          <t>450843</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>860690</t>
+          <t>858531</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>951639</t>
+          <t>953102</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>230063</t>
+          <t>226955</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>285367</t>
+          <t>284060</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>221944</t>
+          <t>225177</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>278600</t>
+          <t>279235</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>469061</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>543928</t>
+          <t>547179</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>124643</t>
+          <t>124275</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>170003</t>
+          <t>171849</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>138070</t>
+          <t>137985</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185264</t>
+          <t>184949</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,47 +1691,47 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
+          <t>14,25%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>19,1%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>306680</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>275213</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>341568</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>15,89%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>14,26%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>19,13%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>306680</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>272701</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>340548</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>15,89%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>14,13%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36753</t>
+          <t>36752</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63840</t>
+          <t>65992</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86684</t>
+          <t>86654</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128016</t>
+          <t>129724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132969</t>
+          <t>131883</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>183472</t>
+          <t>179437</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13831</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34575</t>
+          <t>34072</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21755</t>
+          <t>21486</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43646</t>
+          <t>43603</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38544</t>
+          <t>40670</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70936</t>
+          <t>72671</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>331405</t>
+          <t>332839</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>383545</t>
+          <t>385344</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>314344</t>
+          <t>312884</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>362931</t>
+          <t>364697</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>659812</t>
+          <t>659010</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>734173</t>
+          <t>728604</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,48%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>146988</t>
+          <t>146697</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>192875</t>
+          <t>192922</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>132678</t>
+          <t>132571</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>177027</t>
+          <t>176410</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>291040</t>
+          <t>288831</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>355229</t>
+          <t>351287</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,79%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82260</t>
+          <t>81845</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>118844</t>
+          <t>118891</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>93698</t>
+          <t>92339</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>132634</t>
+          <t>131286</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>184590</t>
+          <t>185499</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>236568</t>
+          <t>236588</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30734</t>
+          <t>30173</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58594</t>
+          <t>57333</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54792</t>
+          <t>54903</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85892</t>
+          <t>87148</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93247</t>
+          <t>92196</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>133485</t>
+          <t>131604</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21526</t>
+          <t>20293</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20261</t>
+          <t>20345</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14021</t>
+          <t>14570</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35136</t>
+          <t>35329</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>440100</t>
+          <t>439540</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>502776</t>
+          <t>498992</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>446091</t>
+          <t>447554</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>508998</t>
+          <t>508642</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>904526</t>
+          <t>903159</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>994055</t>
+          <t>992277</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,09%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>236439</t>
+          <t>234419</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>290063</t>
+          <t>288959</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>245520</t>
+          <t>245054</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>302556</t>
+          <t>301599</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>493049</t>
+          <t>491432</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>573605</t>
+          <t>571478</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>113626</t>
+          <t>114758</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>155332</t>
+          <t>156277</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>127629</t>
+          <t>130040</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>173833</t>
+          <t>173883</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>252024</t>
+          <t>254288</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>316185</t>
+          <t>314552</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>44433</t>
+          <t>43454</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>73461</t>
+          <t>71870</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>92204</t>
+          <t>94106</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>133808</t>
+          <t>135946</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>146450</t>
+          <t>144794</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>198567</t>
+          <t>194683</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12333</t>
+          <t>12462</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33165</t>
+          <t>32148</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17984</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>40100</t>
+          <t>39412</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>34378</t>
+          <t>35163</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>63005</t>
+          <t>62855</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1552239</t>
+          <t>1553434</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1671541</t>
+          <t>1670711</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1435877</t>
+          <t>1426542</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1545112</t>
+          <t>1537396</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3022105</t>
+          <t>3027477</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3187241</t>
+          <t>3189436</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,92%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>884795</t>
+          <t>884953</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>985371</t>
+          <t>989285</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>824918</t>
+          <t>829766</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>922343</t>
+          <t>931684</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1737396</t>
+          <t>1733925</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1881853</t>
+          <t>1885231</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>461265</t>
+          <t>461105</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>544628</t>
+          <t>541415</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>516506</t>
+          <t>520021</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>604491</t>
+          <t>601008</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1003431</t>
+          <t>1002327</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1125701</t>
+          <t>1124936</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>144930</t>
+          <t>147819</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>197410</t>
+          <t>198976</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>341288</t>
+          <t>339168</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>419477</t>
+          <t>414397</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>501855</t>
+          <t>503962</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>595201</t>
+          <t>594344</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>42747</t>
+          <t>42389</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>76429</t>
+          <t>75635</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>62588</t>
+          <t>63505</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>97855</t>
+          <t>99328</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>114849</t>
+          <t>115423</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>162711</t>
+          <t>164540</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>375419</t>
+          <t>375456</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>429864</t>
+          <t>429200</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>293991</t>
+          <t>291791</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>346773</t>
+          <t>346504</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>686541</t>
+          <t>685750</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>763331</t>
+          <t>757082</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,13%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141796</t>
+          <t>141483</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>186356</t>
+          <t>185068</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>176208</t>
+          <t>175766</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>225520</t>
+          <t>224930</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>327645</t>
+          <t>329721</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>394076</t>
+          <t>395461</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75583</t>
+          <t>78057</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112478</t>
+          <t>116642</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62923</t>
+          <t>63404</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>96641</t>
+          <t>98851</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>145814</t>
+          <t>149146</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>199367</t>
+          <t>198426</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15593</t>
+          <t>15838</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33119</t>
+          <t>33392</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47097</t>
+          <t>46180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79536</t>
+          <t>79085</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68250</t>
+          <t>67402</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104476</t>
+          <t>105179</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10484</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29075</t>
+          <t>29328</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27837</t>
+          <t>26750</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52247</t>
+          <t>52403</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42420</t>
+          <t>43621</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72278</t>
+          <t>73742</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>488548</t>
+          <t>489017</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>559157</t>
+          <t>558020</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>414420</t>
+          <t>416376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>482490</t>
+          <t>482755</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>927437</t>
+          <t>923970</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1020741</t>
+          <t>1022090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>243258</t>
+          <t>248338</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>305467</t>
+          <t>307824</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251915</t>
+          <t>253380</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>310430</t>
+          <t>311368</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>516881</t>
+          <t>513643</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>601243</t>
+          <t>600120</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>114835</t>
+          <t>112350</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>160391</t>
+          <t>159537</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>144271</t>
+          <t>146883</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>195438</t>
+          <t>197683</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>272325</t>
+          <t>270764</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>339665</t>
+          <t>340289</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51877</t>
+          <t>52488</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87871</t>
+          <t>89335</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74427</t>
+          <t>74011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113932</t>
+          <t>111630</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134034</t>
+          <t>135183</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>184711</t>
+          <t>186755</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5971</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21457</t>
+          <t>21532</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28534</t>
+          <t>29324</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56119</t>
+          <t>56155</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37443</t>
+          <t>37181</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68552</t>
+          <t>69237</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>365821</t>
+          <t>364027</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>424597</t>
+          <t>423546</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>326662</t>
+          <t>326116</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>385912</t>
+          <t>385382</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>707376</t>
+          <t>710277</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>787010</t>
+          <t>793561</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,82%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152600</t>
+          <t>148152</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201341</t>
+          <t>198739</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>174054</t>
+          <t>170229</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>223334</t>
+          <t>222319</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>338367</t>
+          <t>337203</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>411721</t>
+          <t>406443</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90007</t>
+          <t>90961</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>129818</t>
+          <t>132155</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>89848</t>
+          <t>88899</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>132797</t>
+          <t>128826</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>189603</t>
+          <t>191227</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>250582</t>
+          <t>248511</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34631</t>
+          <t>35117</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63245</t>
+          <t>63541</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60235</t>
+          <t>61204</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>95529</t>
+          <t>93146</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>103921</t>
+          <t>102536</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>146762</t>
+          <t>144973</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16857</t>
+          <t>17965</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41072</t>
+          <t>41821</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26840</t>
+          <t>25419</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52574</t>
+          <t>51807</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48564</t>
+          <t>49021</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>83724</t>
+          <t>86600</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>432839</t>
+          <t>433021</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>495596</t>
+          <t>499090</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>411104</t>
+          <t>411246</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>469594</t>
+          <t>475939</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>857876</t>
+          <t>858616</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>945967</t>
+          <t>950869</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,63%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>254596</t>
+          <t>258096</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>314584</t>
+          <t>315341</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>295345</t>
+          <t>296404</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>353518</t>
+          <t>354527</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>569051</t>
+          <t>565317</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>652398</t>
+          <t>653960</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>96225</t>
+          <t>93804</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>136948</t>
+          <t>136115</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>120377</t>
+          <t>119107</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>167119</t>
+          <t>165799</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>223202</t>
+          <t>224557</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>287301</t>
+          <t>288489</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47917</t>
+          <t>47278</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78640</t>
+          <t>77511</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>68504</t>
+          <t>67856</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103344</t>
+          <t>105488</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>123199</t>
+          <t>126131</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>170695</t>
+          <t>172126</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13583</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>34004</t>
+          <t>32552</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44545</t>
+          <t>44282</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>74462</t>
+          <t>73734</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>65105</t>
+          <t>65098</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>100823</t>
+          <t>100888</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1720768</t>
+          <t>1718947</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1843055</t>
+          <t>1844085</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1500951</t>
+          <t>1508792</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1622202</t>
+          <t>1626832</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3262648</t>
+          <t>3265613</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3431605</t>
+          <t>3436347</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,28%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>847551</t>
+          <t>843446</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>955770</t>
+          <t>957219</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>955232</t>
+          <t>951282</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1064658</t>
+          <t>1059648</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1831517</t>
+          <t>1834126</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1989142</t>
+          <t>1992389</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>415566</t>
+          <t>412281</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>497166</t>
+          <t>496335</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>453479</t>
+          <t>459386</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>540638</t>
+          <t>544119</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>894480</t>
+          <t>893367</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1017251</t>
+          <t>1010288</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>171682</t>
+          <t>174766</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>231044</t>
+          <t>232657</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>278025</t>
+          <t>281440</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>346866</t>
+          <t>350556</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>472649</t>
+          <t>474606</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>561782</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>61789</t>
+          <t>61757</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>101645</t>
+          <t>101300</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>150141</t>
+          <t>149262</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>202524</t>
+          <t>204293</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>223751</t>
+          <t>225030</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>288009</t>
+          <t>290454</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>274538</t>
+          <t>274990</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>325216</t>
+          <t>326349</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>218002</t>
+          <t>217245</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>267515</t>
+          <t>267947</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>504279</t>
+          <t>505409</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>576105</t>
+          <t>578384</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,02%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>195408</t>
+          <t>196438</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>245922</t>
+          <t>243821</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>201423</t>
+          <t>200722</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>252160</t>
+          <t>251300</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>413824</t>
+          <t>410920</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>481561</t>
+          <t>482685</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,9%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81150</t>
+          <t>80107</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117335</t>
+          <t>117131</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>105206</t>
+          <t>105790</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>145148</t>
+          <t>146604</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>197810</t>
+          <t>195769</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251056</t>
+          <t>248643</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39180</t>
+          <t>39507</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67735</t>
+          <t>67354</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39947</t>
+          <t>40623</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69048</t>
+          <t>69356</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87303</t>
+          <t>86993</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>128008</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10530</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17413</t>
+          <t>18064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38152</t>
+          <t>36859</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21246</t>
+          <t>20001</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45420</t>
+          <t>42683</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>413051</t>
+          <t>414928</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>482603</t>
+          <t>480149</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>362322</t>
+          <t>366852</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>427417</t>
+          <t>429518</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>797127</t>
+          <t>802113</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>888081</t>
+          <t>893922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,28%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>329292</t>
+          <t>329567</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>394507</t>
+          <t>397388</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327146</t>
+          <t>326972</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>390186</t>
+          <t>389634</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>676378</t>
+          <t>672179</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>761235</t>
+          <t>765821</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>133386</t>
+          <t>135540</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>181118</t>
+          <t>179148</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>147209</t>
+          <t>145366</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>197949</t>
+          <t>193690</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>294178</t>
+          <t>292877</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>359659</t>
+          <t>360401</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26570</t>
+          <t>26924</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53860</t>
+          <t>52881</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75606</t>
+          <t>75393</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113272</t>
+          <t>114215</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108579</t>
+          <t>109815</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>154743</t>
+          <t>156326</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11004</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28478</t>
+          <t>27558</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17957</t>
+          <t>18352</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40742</t>
+          <t>41667</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32302</t>
+          <t>33451</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58797</t>
+          <t>59816</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>281631</t>
+          <t>279079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>337210</t>
+          <t>335229</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>262163</t>
+          <t>263154</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>316261</t>
+          <t>318707</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>558564</t>
+          <t>557787</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>634621</t>
+          <t>634388</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,23%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>231077</t>
+          <t>230171</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>284524</t>
+          <t>282261</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>234742</t>
+          <t>234974</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>290401</t>
+          <t>292675</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>484001</t>
+          <t>484245</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>557059</t>
+          <t>558154</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>133221</t>
+          <t>133457</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>180166</t>
+          <t>179772</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>148240</t>
+          <t>148005</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>197057</t>
+          <t>195342</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>295684</t>
+          <t>293266</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>362138</t>
+          <t>362357</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20239</t>
+          <t>19474</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43265</t>
+          <t>43057</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24957</t>
+          <t>25257</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48589</t>
+          <t>50336</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50483</t>
+          <t>50394</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83121</t>
+          <t>83072</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>15897</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14357</t>
+          <t>14143</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32801</t>
+          <t>33549</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18511</t>
+          <t>18843</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40817</t>
+          <t>40631</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>368991</t>
+          <t>367114</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>428392</t>
+          <t>431549</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>388385</t>
+          <t>391746</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>454213</t>
+          <t>457970</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>779857</t>
+          <t>773141</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>863663</t>
+          <t>865886</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,78%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>269653</t>
+          <t>267206</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>327365</t>
+          <t>329062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>284379</t>
+          <t>284269</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>345386</t>
+          <t>345633</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>573822</t>
+          <t>573138</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>651754</t>
+          <t>657054</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,22%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>136672</t>
+          <t>136135</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>182058</t>
+          <t>181689</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>140301</t>
+          <t>140065</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>188524</t>
+          <t>189694</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>289248</t>
+          <t>288509</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>354675</t>
+          <t>359201</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36223</t>
+          <t>35770</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65373</t>
+          <t>63510</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72777</t>
+          <t>74262</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>111877</t>
+          <t>111485</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>118258</t>
+          <t>117971</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>165131</t>
+          <t>166628</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19814</t>
+          <t>20226</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42583</t>
+          <t>44482</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37736</t>
+          <t>37615</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66204</t>
+          <t>66512</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>64674</t>
+          <t>64718</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>101121</t>
+          <t>99792</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1397430</t>
+          <t>1393143</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1518844</t>
+          <t>1507590</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1286044</t>
+          <t>1284107</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1404218</t>
+          <t>1401994</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2709268</t>
+          <t>2716389</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2886524</t>
+          <t>2890478</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1075684</t>
+          <t>1080681</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1191980</t>
+          <t>1197292</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1102896</t>
+          <t>1106538</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1214845</t>
+          <t>1216497</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2218121</t>
+          <t>2214324</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2380763</t>
+          <t>2384780</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,43%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>524017</t>
+          <t>527640</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>617280</t>
+          <t>615243</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>581978</t>
+          <t>580599</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>673659</t>
+          <t>679270</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1137275</t>
+          <t>1133750</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1265182</t>
+          <t>1264381</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>143340</t>
+          <t>144808</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>195723</t>
+          <t>195657</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>241627</t>
+          <t>241551</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>307298</t>
+          <t>306384</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>407101</t>
+          <t>399331</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>487219</t>
+          <t>485432</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>44806</t>
+          <t>44084</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>75097</t>
+          <t>76566</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>105625</t>
+          <t>104229</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>150510</t>
+          <t>151761</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>156460</t>
+          <t>159447</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>213448</t>
+          <t>213405</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -11654,32 +11654,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>368555</t>
+          <t>394049</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>339583</t>
+          <t>364881</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>393945</t>
+          <t>423121</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11689,32 +11689,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>356550</t>
+          <t>385875</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>338031</t>
+          <t>366084</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>377379</t>
+          <t>410024</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11724,32 +11724,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>725105</t>
+          <t>779925</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>692120</t>
+          <t>746121</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>759717</t>
+          <t>812083</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>57,16%</t>
         </is>
       </c>
     </row>
@@ -11767,32 +11767,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>161048</t>
+          <t>176202</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>140367</t>
+          <t>153805</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>185744</t>
+          <t>200634</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,32 +11802,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>197296</t>
+          <t>214389</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178368</t>
+          <t>195280</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>215055</t>
+          <t>235083</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,32 +11837,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>358344</t>
+          <t>390591</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>331197</t>
+          <t>360958</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>389343</t>
+          <t>422445</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>70953</t>
+          <t>78897</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55662</t>
+          <t>61363</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>89490</t>
+          <t>96901</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>76292</t>
+          <t>81355</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>65116</t>
+          <t>69031</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>87943</t>
+          <t>95120</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>147245</t>
+          <t>160252</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>128242</t>
+          <t>140143</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>168143</t>
+          <t>184203</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -11993,32 +11993,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22325</t>
+          <t>26287</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14811</t>
+          <t>16544</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32159</t>
+          <t>36417</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34120</t>
+          <t>38006</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26345</t>
+          <t>29724</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43894</t>
+          <t>48549</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,32 +12063,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>56445</t>
+          <t>64293</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45298</t>
+          <t>51133</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68846</t>
+          <t>78858</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -12106,32 +12106,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>14461</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18855</t>
+          <t>24099</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>11199</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14360</t>
+          <t>16685</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>21192</t>
+          <t>25660</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15397</t>
+          <t>18553</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29695</t>
+          <t>36481</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>634642</t>
+          <t>689896</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>634642</t>
+          <t>689896</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>634642</t>
+          <t>689896</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>673689</t>
+          <t>730824</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>673689</t>
+          <t>730824</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>673689</t>
+          <t>730824</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1308331</t>
+          <t>1420720</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1308331</t>
+          <t>1420720</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1308331</t>
+          <t>1420720</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,32 +12336,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>782312</t>
+          <t>588426</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>658971</t>
+          <t>554878</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>990557</t>
+          <t>627771</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12371,32 +12371,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>512056</t>
+          <t>563007</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>483267</t>
+          <t>534204</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>537218</t>
+          <t>591249</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,32 +12406,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1294368</t>
+          <t>1151434</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1167664</t>
+          <t>1103554</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1587735</t>
+          <t>1196839</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>56,62%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>279602</t>
+          <t>301242</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>140107</t>
+          <t>266880</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>367228</t>
+          <t>334451</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>262178</t>
+          <t>299536</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>241818</t>
+          <t>274758</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>285451</t>
+          <t>326676</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>541780</t>
+          <t>600778</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>360565</t>
+          <t>556942</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>624434</t>
+          <t>641888</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74210</t>
+          <t>90070</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35172</t>
+          <t>73443</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>101212</t>
+          <t>110313</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,32 +12597,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>106083</t>
+          <t>118563</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>93030</t>
+          <t>103303</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>123160</t>
+          <t>136680</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>180293</t>
+          <t>208634</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115176</t>
+          <t>183903</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>215376</t>
+          <t>236827</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32435</t>
+          <t>41572</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15338</t>
+          <t>29529</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50073</t>
+          <t>58635</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>55294</t>
+          <t>64451</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43542</t>
+          <t>52670</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69331</t>
+          <t>80865</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>87729</t>
+          <t>106024</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61199</t>
+          <t>88094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110794</t>
+          <t>128328</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -12788,32 +12788,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>23260</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>14522</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32799</t>
+          <t>35667</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,32 +12823,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21408</t>
+          <t>23590</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14239</t>
+          <t>16064</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32759</t>
+          <t>35151</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12858,32 +12858,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>41698</t>
+          <t>46850</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26303</t>
+          <t>34889</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57413</t>
+          <t>61492</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1188849</t>
+          <t>1044571</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1188849</t>
+          <t>1044571</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1188849</t>
+          <t>1044571</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>957018</t>
+          <t>1069148</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>957018</t>
+          <t>1069148</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>957018</t>
+          <t>1069148</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2145867</t>
+          <t>2113719</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2145867</t>
+          <t>2113719</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2145867</t>
+          <t>2113719</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13018,32 +13018,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>391419</t>
+          <t>431547</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>360349</t>
+          <t>397363</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>422831</t>
+          <t>461136</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13053,32 +13053,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>376905</t>
+          <t>399056</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>346639</t>
+          <t>369617</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>428945</t>
+          <t>426289</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13088,32 +13088,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>768324</t>
+          <t>830603</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>726446</t>
+          <t>786677</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>817447</t>
+          <t>874696</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>54,37%</t>
         </is>
       </c>
     </row>
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>204325</t>
+          <t>228310</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177548</t>
+          <t>202598</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>233160</t>
+          <t>260325</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>228925</t>
+          <t>262811</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>195387</t>
+          <t>238327</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>254719</t>
+          <t>288453</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>433249</t>
+          <t>491121</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>393649</t>
+          <t>454164</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>472992</t>
+          <t>533101</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>76531</t>
+          <t>100354</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58894</t>
+          <t>80195</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>99104</t>
+          <t>126124</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>70555</t>
+          <t>85861</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54220</t>
+          <t>69182</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>91438</t>
+          <t>105424</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,32 +13314,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>147086</t>
+          <t>186215</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>122413</t>
+          <t>158579</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>176425</t>
+          <t>215581</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22752</t>
+          <t>29624</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15005</t>
+          <t>19951</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33275</t>
+          <t>41761</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,32 +13392,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38511</t>
+          <t>44993</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28083</t>
+          <t>34747</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49250</t>
+          <t>56112</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13427,32 +13427,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>61263</t>
+          <t>74617</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49643</t>
+          <t>60722</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76576</t>
+          <t>91845</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -13470,32 +13470,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14171</t>
+          <t>16303</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13505,32 +13505,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12596</t>
+          <t>17423</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7979</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19582</t>
+          <t>26933</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>20021</t>
+          <t>26105</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13237</t>
+          <t>18035</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28375</t>
+          <t>38548</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>702451</t>
+          <t>798518</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>702451</t>
+          <t>798518</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>702451</t>
+          <t>798518</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>727492</t>
+          <t>810144</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>727492</t>
+          <t>810144</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>727492</t>
+          <t>810144</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1429943</t>
+          <t>1608662</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1429943</t>
+          <t>1608662</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1429943</t>
+          <t>1608662</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>562827</t>
+          <t>595278</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>529999</t>
+          <t>561881</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>591981</t>
+          <t>624122</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13735,32 +13735,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>623067</t>
+          <t>596888</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>581365</t>
+          <t>567725</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>709823</t>
+          <t>625116</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,32 +13770,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1185894</t>
+          <t>1192167</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1135959</t>
+          <t>1148065</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1281686</t>
+          <t>1234152</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>188389</t>
+          <t>202206</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>166537</t>
+          <t>179143</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>215363</t>
+          <t>227327</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>238946</t>
+          <t>263970</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>191568</t>
+          <t>238500</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>267542</t>
+          <t>288206</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>427336</t>
+          <t>466176</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>373775</t>
+          <t>429944</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>465491</t>
+          <t>502231</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -13926,32 +13926,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>103648</t>
+          <t>112785</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>84955</t>
+          <t>93703</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>125374</t>
+          <t>136812</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>113349</t>
+          <t>123467</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>87342</t>
+          <t>106607</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>131740</t>
+          <t>140240</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>216997</t>
+          <t>236252</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>187902</t>
+          <t>208308</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>245043</t>
+          <t>266982</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -14039,32 +14039,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>43513</t>
+          <t>48083</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33071</t>
+          <t>36278</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57060</t>
+          <t>62307</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14074,32 +14074,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>69244</t>
+          <t>80535</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55206</t>
+          <t>65389</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>85190</t>
+          <t>95999</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>112757</t>
+          <t>128618</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>93667</t>
+          <t>110903</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>130487</t>
+          <t>149188</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -14152,32 +14152,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17176</t>
+          <t>19821</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35799</t>
+          <t>41102</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14187,67 +14187,67 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>45208</t>
+          <t>48088</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33118</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>63517</t>
+          <t>60638</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>5,45%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>77137</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>63772</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>91736</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>3,04%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>71072</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>57267</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>91683</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>924241</t>
+          <t>987401</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>924241</t>
+          <t>987401</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>924241</t>
+          <t>987401</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1089815</t>
+          <t>1112949</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1089815</t>
+          <t>1112949</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1089815</t>
+          <t>1112949</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2014056</t>
+          <t>2100350</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2014056</t>
+          <t>2100350</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2014056</t>
+          <t>2100350</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,32 +14382,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2105112</t>
+          <t>2009301</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1989083</t>
+          <t>1944202</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2438418</t>
+          <t>2070211</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14417,32 +14417,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1868579</t>
+          <t>1944827</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1805936</t>
+          <t>1886330</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1985492</t>
+          <t>1997434</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14452,32 +14452,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3973691</t>
+          <t>3954127</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3823419</t>
+          <t>3873824</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4325219</t>
+          <t>4036898</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>55,73%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>833365</t>
+          <t>907960</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>630210</t>
+          <t>855750</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>915099</t>
+          <t>963308</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,67 +14530,67 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>927345</t>
+          <t>1040705</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>855267</t>
+          <t>993430</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>975872</t>
+          <t>1089584</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
+          <t>27,95%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>26,68%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>29,27%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>2538</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>1948665</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>1880326</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>2023252</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>26,9%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>24,8%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>2538</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>1760709</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>1542117</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>1862232</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>25,52%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -14608,32 +14608,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>325342</t>
+          <t>382107</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>249390</t>
+          <t>341186</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>365875</t>
+          <t>422870</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14643,32 +14643,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>366278</t>
+          <t>409246</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>333724</t>
+          <t>376511</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>400651</t>
+          <t>443563</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>691620</t>
+          <t>791353</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>604719</t>
+          <t>745989</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>746805</t>
+          <t>846085</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>121025</t>
+          <t>145567</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>94461</t>
+          <t>124897</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>144146</t>
+          <t>174194</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>197170</t>
+          <t>227985</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>175532</t>
+          <t>204463</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>221134</t>
+          <t>252631</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>318194</t>
+          <t>373552</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>278291</t>
+          <t>339974</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>356551</t>
+          <t>408823</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>65340</t>
+          <t>75451</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>48460</t>
+          <t>60680</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>81893</t>
+          <t>95479</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>88643</t>
+          <t>100301</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>72890</t>
+          <t>85536</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>108566</t>
+          <t>119696</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>153982</t>
+          <t>175752</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>127982</t>
+          <t>153298</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>181754</t>
+          <t>202907</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3450183</t>
+          <t>3520386</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3450183</t>
+          <t>3520386</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3450183</t>
+          <t>3520386</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3448014</t>
+          <t>3723065</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3448014</t>
+          <t>3723065</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3448014</t>
+          <t>3723065</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>6898197</t>
+          <t>7243450</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>6898197</t>
+          <t>7243450</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6898197</t>
+          <t>7243450</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
